--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY162"/>
+  <dimension ref="A1:AZ162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127891285</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59898376</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123728334</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131317908</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/48844056</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81955712</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/29547568</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1602,6 +1642,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/52558643</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1712,6 +1757,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83289441</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83292846</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1928,6 +1983,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/155856</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2030,6 +2090,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/784668</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2132,6 +2197,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1339688</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2256,6 +2326,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109300094</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2374,6 +2449,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66307157</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2492,6 +2572,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66307412</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2610,6 +2695,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66307105</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2725,6 +2815,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101450839</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2836,6 +2931,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15791499</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2959,6 +3059,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109769420</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3078,6 +3183,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133514368</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3197,6 +3307,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109300119</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3325,6 +3440,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109769426</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3440,6 +3560,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109769427</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3555,6 +3680,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101450840</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3673,6 +3803,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66307484</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3775,6 +3910,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3376492</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3882,6 +4022,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71797073</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3984,6 +4129,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3925934</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4086,6 +4236,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3931649</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4188,6 +4343,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4239691</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4290,6 +4450,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4943260</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4397,6 +4562,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71797074</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4494,6 +4664,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135482731</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4591,6 +4766,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80925</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4702,6 +4882,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/175752</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4814,6 +4999,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103706964</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4925,6 +5115,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/196151</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5036,6 +5231,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137930</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5133,6 +5333,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/138495</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5241,6 +5446,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103706985</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5352,6 +5562,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/280152</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5463,6 +5678,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406671</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5565,6 +5785,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/274549</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5662,6 +5887,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/275061</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5773,6 +6003,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/967056</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5884,6 +6119,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1017458</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5995,6 +6235,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1090894</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6096,6 +6341,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111745066</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6208,6 +6458,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103707019</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6324,6 +6579,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1149446</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6435,6 +6695,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1150056</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6537,6 +6802,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1294429</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6652,6 +6922,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103706966</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6764,6 +7039,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103706999</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6871,6 +7151,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1554694</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7010,6 +7295,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112583691</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7114,6 +7404,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54659832</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7233,6 +7528,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97717726</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7352,6 +7652,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106875337</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7471,6 +7776,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114323998</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7580,6 +7890,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121810498</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7699,6 +8014,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100473625</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7818,6 +8138,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75436384</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7932,6 +8257,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89697615</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8051,6 +8381,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84219512</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8170,6 +8505,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75436368</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8289,6 +8629,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75947169</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8390,6 +8735,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122283190</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8505,6 +8855,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75988644</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8624,6 +8979,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75934893</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8735,6 +9095,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114067525</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8864,6 +9229,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68054718</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8972,6 +9342,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54633705</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9074,6 +9449,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100277499</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9176,6 +9556,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100277501</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9286,6 +9671,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83284444</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9396,6 +9786,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83285624</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9506,6 +9901,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83286445</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9616,6 +10016,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83287972</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9726,6 +10131,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83290703</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9836,6 +10246,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83291742</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9946,6 +10361,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83293138</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10056,6 +10476,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83294355</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10166,6 +10591,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83297251</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10276,6 +10706,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83300065</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10386,6 +10821,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83302074</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10488,6 +10928,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100277518</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10604,6 +11049,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103707008</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10706,6 +11156,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100277497</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10822,6 +11277,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5029807</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10924,6 +11384,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100277516</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11035,6 +11500,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103707009</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11137,6 +11607,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100277508</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11239,6 +11714,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100277517</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11351,6 +11831,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6558911</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11452,6 +11937,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126734620</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11551,6 +12041,11 @@
       <c r="AY99" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126734612</t>
         </is>
       </c>
     </row>
@@ -11653,6 +12148,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67615338</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11754,6 +12254,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126734803</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11870,6 +12375,11 @@
           <t>Övervakning av lavar på ek Södermanland 2002</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15928783</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11984,6 +12494,11 @@
       <c r="AY103" t="inlineStr">
         <is>
           <t>Övervakning av lavar på ek Södermanland 2002</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15928784</t>
         </is>
       </c>
     </row>
@@ -12101,6 +12616,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129036179</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12214,6 +12734,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13196831</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12335,6 +12860,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13386943</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12437,6 +12967,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/238859</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12539,6 +13074,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6742301</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12641,6 +13181,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/173861</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12757,6 +13302,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/442832</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12856,6 +13406,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100773306</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12954,6 +13509,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100773163</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13070,6 +13630,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1998594</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13182,6 +13747,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2218050</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13296,6 +13866,11 @@
       <c r="AY115" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1889606</t>
         </is>
       </c>
     </row>
@@ -13403,6 +13978,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113866034</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13522,6 +14102,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830804</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13631,6 +14216,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115244853</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13733,6 +14323,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724525</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13835,6 +14430,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724527</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13952,6 +14552,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129122868</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14068,6 +14673,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117828088</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14179,6 +14789,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346823</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14298,6 +14913,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94211618</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14413,6 +15033,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830809</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14526,6 +15151,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107952918</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14631,6 +15261,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115244971</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14742,6 +15377,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324847</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14849,6 +15489,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105600041</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14964,6 +15609,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346825</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15075,6 +15725,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830812</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15190,6 +15845,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346829</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15295,6 +15955,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114574185</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15410,6 +16075,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129324854</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15519,6 +16189,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115244844</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15635,6 +16310,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15568996</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15750,6 +16430,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132346810</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15852,6 +16537,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3435921</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15972,6 +16662,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132651080</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16074,6 +16769,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5735537</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16186,6 +16886,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124500</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16298,6 +17003,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2218048</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16418,6 +17128,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454863</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16541,6 +17256,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97693684</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16650,6 +17370,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97928276</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16769,6 +17494,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101008353</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16892,6 +17622,11 @@
           <t>Ekoskådning</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108591177</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17015,6 +17750,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101008324</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17120,6 +17860,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99396056</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17225,6 +17970,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101145945</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17348,6 +18098,11 @@
           <t>Ekoskådning</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106006049</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17467,6 +18222,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98383588</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17586,6 +18346,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97693693</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17705,6 +18470,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98383581</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17802,6 +18572,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128193184</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17918,6 +18693,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6740853</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18039,6 +18819,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96212364</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18155,6 +18940,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/431055</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18270,6 +19060,11 @@
           <t>Nordens Ark - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120123778</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18393,6 +19188,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124575936</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18518,6 +19318,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127919799</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18633,8 +19438,176 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118850750</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -4573,7 +4573,7 @@
         <v>135482731</v>
       </c>
       <c r="B35" t="n">
-        <v>103482</v>
+        <v>103533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -4573,7 +4573,7 @@
         <v>135482731</v>
       </c>
       <c r="B35" t="n">
-        <v>103533</v>
+        <v>103560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -4573,7 +4573,7 @@
         <v>135482731</v>
       </c>
       <c r="B35" t="n">
-        <v>103565</v>
+        <v>103567</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -4573,7 +4573,7 @@
         <v>135482731</v>
       </c>
       <c r="B35" t="n">
-        <v>103567</v>
+        <v>103587</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 2932-2024 artfynd.xlsx
+++ b/artfynd/S 2932-2024 artfynd.xlsx
@@ -4573,7 +4573,7 @@
         <v>135482731</v>
       </c>
       <c r="B35" t="n">
-        <v>103587</v>
+        <v>103589</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
